--- a/main/ig/StructureDefinition-fr-observation-vital-signs-document.xlsx
+++ b/main/ig/StructureDefinition-fr-observation-vital-signs-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T11:53:23+00:00</t>
+    <t>2026-09-18T08:26:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-observation-vital-signs-document.xlsx
+++ b/main/ig/StructureDefinition-fr-observation-vital-signs-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-18T08:26:19+00:00</t>
+    <t>2026-09-24T07:33:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-observation-vital-signs-document.xlsx
+++ b/main/ig/StructureDefinition-fr-observation-vital-signs-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-24T07:33:45+00:00</t>
+    <t>2026-09-30T20:06:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1078,7 +1078,7 @@
     <t>5. SHALL contain exactly one [1..1] code, where the @code SHOULD be selected from ValueSet HITSP Vital Sign Result Type 2.16.840.1.113883.3.88.12.80.62 DYNAMIC (CONF:7301).</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-signe-vital-cisis|20260716085853</t>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-signe-vital-cisis|20260916095457</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -1363,7 +1363,7 @@
     <t>For some results, particularly numeric results, an interpretation is necessary to fully understand the significance of a result.</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-hl7-v3-ObservationInterpretation-cisis|20260716085852</t>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-hl7-v3-ObservationInterpretation-cisis|20260916095455</t>
   </si>
   <si>
     <t>&lt; 260245000 |Findings values|</t>

--- a/main/ig/StructureDefinition-fr-observation-vital-signs-document.xlsx
+++ b/main/ig/StructureDefinition-fr-observation-vital-signs-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T20:06:50+00:00</t>
+    <t>2026-10-01T08:49:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-observation-vital-signs-document.xlsx
+++ b/main/ig/StructureDefinition-fr-observation-vital-signs-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T08:49:37+00:00</t>
+    <t>2026-10-01T13:34:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-observation-vital-signs-document.xlsx
+++ b/main/ig/StructureDefinition-fr-observation-vital-signs-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T13:34:48+00:00</t>
+    <t>2026-10-05T07:58:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
